--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\ATR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B374E1-F24D-4177-A4B2-E668D1ED97DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C602D95-D84F-4A4A-90DA-73D5F1432AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="79">
   <si>
     <t>Company Name</t>
   </si>
@@ -8710,7 +8710,7 @@
         <v>46176.474652777775</v>
       </c>
       <c r="J267">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K267" t="s">
         <v>11</v>
@@ -8742,7 +8742,7 @@
         <v>46176.475347222222</v>
       </c>
       <c r="J268">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K268" t="s">
         <v>11</v>
@@ -8774,7 +8774,7 @@
         <v>46176.460185185184</v>
       </c>
       <c r="J269">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K269" t="s">
         <v>11</v>
@@ -8838,7 +8838,7 @@
         <v>46176.460879629631</v>
       </c>
       <c r="J271">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K271" t="s">
         <v>11</v>
@@ -8934,7 +8934,7 @@
         <v>46176.462268518517</v>
       </c>
       <c r="J274">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K274" t="s">
         <v>11</v>
@@ -8966,7 +8966,7 @@
         <v>46176.462962962964</v>
       </c>
       <c r="J275">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K275" t="s">
         <v>11</v>
@@ -8998,7 +8998,7 @@
         <v>46176.462962962964</v>
       </c>
       <c r="J276">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K276" t="s">
         <v>11</v>
@@ -9030,7 +9030,7 @@
         <v>46176.46365740741</v>
       </c>
       <c r="J277">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K277" t="s">
         <v>11</v>
@@ -9062,7 +9062,7 @@
         <v>46176.46365740741</v>
       </c>
       <c r="J278">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K278" t="s">
         <v>11</v>
@@ -9094,7 +9094,7 @@
         <v>46176.46435185185</v>
       </c>
       <c r="J279">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K279" t="s">
         <v>11</v>
@@ -9126,7 +9126,7 @@
         <v>46176.46435185185</v>
       </c>
       <c r="J280">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K280" t="s">
         <v>11</v>
@@ -9158,7 +9158,7 @@
         <v>46176.465740740743</v>
       </c>
       <c r="J281">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K281" t="s">
         <v>11</v>
@@ -9190,7 +9190,7 @@
         <v>46176.465740740743</v>
       </c>
       <c r="J282">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K282" t="s">
         <v>11</v>
@@ -9222,7 +9222,7 @@
         <v>46176.465740740743</v>
       </c>
       <c r="J283">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K283" t="s">
         <v>11</v>
@@ -9309,16 +9309,16 @@
         <v>25</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H286" s="2">
-        <v>0</v>
+        <v>6.9560185185185185E-3</v>
       </c>
       <c r="I286" s="1">
         <v>46176.467129629629</v>
       </c>
       <c r="J286">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K286" t="s">
         <v>11</v>
@@ -9350,7 +9350,7 @@
         <v>46176.467129629629</v>
       </c>
       <c r="J287">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K287" t="s">
         <v>11</v>
@@ -9382,7 +9382,7 @@
         <v>46176.467824074076</v>
       </c>
       <c r="J288">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K288" t="s">
         <v>11</v>
@@ -9414,7 +9414,7 @@
         <v>46176.467824074076</v>
       </c>
       <c r="J289">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K289" t="s">
         <v>11</v>
@@ -9446,7 +9446,7 @@
         <v>46176.468518518515</v>
       </c>
       <c r="J290">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K290" t="s">
         <v>11</v>
@@ -9478,7 +9478,7 @@
         <v>46176.468518518515</v>
       </c>
       <c r="J291">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K291" t="s">
         <v>11</v>
@@ -9501,7 +9501,7 @@
         <v>25</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H292" s="2">
         <v>0</v>
@@ -9510,60 +9510,83 @@
         <v>46176.468518518515</v>
       </c>
       <c r="J292">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K292" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="293" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F293" s="2"/>
-      <c r="G293" s="1"/>
-      <c r="H293" s="2"/>
-      <c r="I293" s="1"/>
+      <c r="B293" t="s">
+        <v>27</v>
+      </c>
+      <c r="C293">
+        <v>5370</v>
+      </c>
+      <c r="D293" t="s">
+        <v>52</v>
+      </c>
+      <c r="E293" t="s">
+        <v>52</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H293" s="2">
+        <v>5.9606481481481481E-3</v>
+      </c>
+      <c r="I293" s="1">
+        <v>46176.469212962962</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
       <c r="K293" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F294" s="2"/>
+      <c r="G294" s="1"/>
+      <c r="H294" s="2"/>
+      <c r="I294" s="1"/>
+      <c r="K294" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B294" t="s">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B295" t="s">
         <v>27</v>
       </c>
-      <c r="C294">
-        <v>5370</v>
-      </c>
-      <c r="D294" t="s">
+      <c r="C295">
+        <v>5371</v>
+      </c>
+      <c r="D295" t="s">
+        <v>66</v>
+      </c>
+      <c r="E295" t="s">
         <v>52</v>
       </c>
-      <c r="E294" t="s">
-        <v>52</v>
-      </c>
-      <c r="F294" s="2" t="s">
+      <c r="F295" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G294" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H294" s="2">
-        <v>7.407407407407407E-4</v>
-      </c>
-      <c r="I294" s="1">
+      <c r="G295" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H295" s="2">
+        <v>0</v>
+      </c>
+      <c r="I295" s="1">
         <v>46176.469212962962</v>
       </c>
-      <c r="J294">
-        <v>0</v>
-      </c>
-      <c r="K294" t="s">
+      <c r="J295">
+        <v>3</v>
+      </c>
+      <c r="K295" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F295" s="2"/>
-      <c r="G295" s="1"/>
-      <c r="H295" s="2"/>
-      <c r="I295" s="1"/>
-      <c r="K295" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="296" spans="2:11" x14ac:dyDescent="0.25">
@@ -9571,13 +9594,13 @@
         <v>27</v>
       </c>
       <c r="C296">
-        <v>5371</v>
+        <v>4704</v>
       </c>
       <c r="D296" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E296" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>25</v>
@@ -9589,46 +9612,20 @@
         <v>0</v>
       </c>
       <c r="I296" s="1">
-        <v>46176.469212962962</v>
+        <v>46176.469907407409</v>
       </c>
       <c r="J296">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K296" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B297" t="s">
-        <v>27</v>
-      </c>
-      <c r="C297">
-        <v>4704</v>
-      </c>
-      <c r="D297" t="s">
-        <v>49</v>
-      </c>
-      <c r="E297" t="s">
-        <v>33</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H297" s="2">
-        <v>0</v>
-      </c>
-      <c r="I297" s="1">
-        <v>46176.469907407409</v>
-      </c>
-      <c r="J297">
-        <v>1</v>
-      </c>
-      <c r="K297" t="s">
-        <v>11</v>
-      </c>
+      <c r="F297" s="2"/>
+      <c r="G297" s="1"/>
+      <c r="H297" s="2"/>
+      <c r="I297" s="1"/>
     </row>
     <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F298" s="2"/>
